--- a/Casos de Regatas.xlsx
+++ b/Casos de Regatas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b358109354d87fd/Diplomaturas/Inteligencia Artificial Aplicada/Materias/04. Procesamiento de Lenguaje Natural/TP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b358109354d87fd/Diplomaturas/Inteligencia Artificial Aplicada/Materias/04. Procesamiento de Lenguaje Natural/DIIA-PLN-TP-Final/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="94" documentId="11_2C447A9E1C490587C5EB8AD627D4F21B5C78B259" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3196FA3D-900A-CA43-8597-A93AD75CEBA2}"/>
   <bookViews>
-    <workbookView xWindow="34100" yWindow="2200" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="880" windowWidth="34540" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Casos de Regatas y sus Títulos" sheetId="1" r:id="rId1"/>
@@ -1572,10 +1572,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Casos de Regatas.xlsx
+++ b/Casos de Regatas.xlsx
@@ -1,26 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b358109354d87fd/Diplomaturas/Inteligencia Artificial Aplicada/Materias/04. Procesamiento de Lenguaje Natural/DIIA-PLN-TP-Final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b358109354d87fd/Diplomaturas/01. Inteligencia Artificial Aplicada/Materias/04. Procesamiento de Lenguaje Natural/99. DIIA-PLN-TP-Final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="11_2C447A9E1C490587C5EB8AD627D4F21B5C78B259" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3196FA3D-900A-CA43-8597-A93AD75CEBA2}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="11_2C447A9E1C490587C5EB8AD627D4F21B5C78B259" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D593CC31-402B-2B4B-B0DA-6A9493322C0C}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="880" windowWidth="34540" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33680" yWindow="1940" windowWidth="33660" windowHeight="17360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Casos de Regatas y sus Títulos" sheetId="1" r:id="rId1"/>
+    <sheet name="Resultados" sheetId="2" r:id="rId2"/>
+    <sheet name="Análisis" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -1457,13 +1472,80 @@
       </rPr>
       <t>: Penalizar a B.</t>
     </r>
+  </si>
+  <si>
+    <t>Prompt Español</t>
+  </si>
+  <si>
+    <t>Prompt inglés</t>
+  </si>
+  <si>
+    <t>Chain-of-Thought (CoT)</t>
+  </si>
+  <si>
+    <t>Few-Shot 
+Chain-of-Thought (FS CoT)</t>
+  </si>
+  <si>
+    <t>Comentarios</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>Falla</t>
+  </si>
+  <si>
+    <t>CoT - ES: El resultado es correcto, pero el modelo alucina en el rationale y en la regla aplicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoT - ES: Solo aplica la regla 11 pero no aplica la regla 16.1 </t>
+  </si>
+  <si>
+    <t>CoT - EN:</t>
+  </si>
+  <si>
+    <t>FS CoT - ES:</t>
+  </si>
+  <si>
+    <t>FS CoT - EN:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoT - ES: </t>
+  </si>
+  <si>
+    <t>CoT - ES: Alucina en el rationale y con las reglas</t>
+  </si>
+  <si>
+    <t>CoT - ES: El modelo interpreta el escenario de manera particular (asume que el barco B completó la virada)</t>
+  </si>
+  <si>
+    <t>CoT - ES: No explicita todas las reglas que deberían considerarse</t>
+  </si>
+  <si>
+    <t>CoT - ES: El modelo asume que el barco Y vira y choca</t>
+  </si>
+  <si>
+    <t>CoT - ES: Las reglas mencionadas no se ajustan al Ground Thruth</t>
+  </si>
+  <si>
+    <t>CoT - ES: Identifica bien la regla, pero interpreta mal los puntos de aplicación</t>
+  </si>
+  <si>
+    <t>CoT - ES: El modelo asume que B choca, y toma la decisión correcta penalizando. La reglas de aplicación tienen sentido</t>
+  </si>
+  <si>
+    <t>CoT - ES: El análisis de modelo es correcto, pero hay una "zona gris" del escenario que probablemente causa confusión</t>
+  </si>
+  <si>
+    <t>CoT - ES: Razonamiento incorrecto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1500,6 +1582,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1515,7 +1603,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1538,11 +1626,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1557,9 +1764,77 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2011,4 +2286,812 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CDA499-0016-9E48-AD79-F5B2F70F2B84}">
+  <dimension ref="A1:G64"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="85.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="3" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="B4" s="11"/>
+      <c r="C4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B6" s="15"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B7" s="15"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B8" s="16"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B9" s="14">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B10" s="15"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B11" s="15"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B13" s="14">
+        <v>3</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B14" s="15"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B15" s="15"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B16" s="16"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="28" x14ac:dyDescent="0.15">
+      <c r="B17" s="14">
+        <v>4</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B18" s="15"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B19" s="15"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B20" s="16"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B21" s="19">
+        <v>5</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B22" s="20"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B23" s="20"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B24" s="21"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B25" s="19">
+        <v>6</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B26" s="20"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B27" s="20"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B28" s="23"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B29" s="24">
+        <v>7</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B30" s="20"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B31" s="20"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B32" s="23"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B33" s="24">
+        <v>8</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B34" s="20"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B35" s="20"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B36" s="23"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="28" x14ac:dyDescent="0.15">
+      <c r="B37" s="24">
+        <v>9</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B38" s="20"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B39" s="20"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B40" s="23"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="28" x14ac:dyDescent="0.15">
+      <c r="B41" s="24">
+        <v>10</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B42" s="20"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B43" s="20"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B44" s="23"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B45" s="24">
+        <v>11</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B46" s="20"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B47" s="20"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B48" s="23"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B49" s="24">
+        <v>12</v>
+      </c>
+      <c r="C49" s="17"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B50" s="20"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B51" s="20"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B52" s="23"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B53" s="24">
+        <v>13</v>
+      </c>
+      <c r="C53" s="17"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B54" s="20"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B55" s="20"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B56" s="23"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B57" s="24">
+        <v>14</v>
+      </c>
+      <c r="C57" s="17"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B58" s="20"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B59" s="20"/>
+      <c r="C59" s="17"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B60" s="23"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B61" s="24">
+        <v>15</v>
+      </c>
+      <c r="C61" s="17"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B62" s="20"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B63" s="20"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="B64" s="23"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="79">
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="B57:B60"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="D57:D60"/>
+    <mergeCell ref="E57:E60"/>
+    <mergeCell ref="F57:F60"/>
+    <mergeCell ref="B61:B64"/>
+    <mergeCell ref="C61:C64"/>
+    <mergeCell ref="D61:D64"/>
+    <mergeCell ref="E61:E64"/>
+    <mergeCell ref="F61:F64"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="C49:C52"/>
+    <mergeCell ref="D49:D52"/>
+    <mergeCell ref="E49:E52"/>
+    <mergeCell ref="F49:F52"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="C53:C56"/>
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="E53:E56"/>
+    <mergeCell ref="F53:F56"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="D41:D44"/>
+    <mergeCell ref="E41:E44"/>
+    <mergeCell ref="F41:F44"/>
+    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="C45:C48"/>
+    <mergeCell ref="D45:D48"/>
+    <mergeCell ref="E45:E48"/>
+    <mergeCell ref="F45:F48"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="C33:C36"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="E33:E36"/>
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="C37:C40"/>
+    <mergeCell ref="D37:D40"/>
+    <mergeCell ref="E37:E40"/>
+    <mergeCell ref="F37:F40"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="E25:E28"/>
+    <mergeCell ref="F25:F28"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="D29:D32"/>
+    <mergeCell ref="E29:E32"/>
+    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="E17:E20"/>
+    <mergeCell ref="F17:F20"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="F13:F16"/>
+    <mergeCell ref="B5:B8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED012409-1330-4547-82DA-5BA50D4F7AB8}">
+  <dimension ref="E6:K13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="6" spans="5:11" x14ac:dyDescent="0.15">
+      <c r="E6" s="28">
+        <f>COUNTIF(Resultados!C$5:C$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="F6" s="28">
+        <f>COUNTIF(Resultados!C$5:C$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="5:11" x14ac:dyDescent="0.15">
+      <c r="K13" s="28"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Casos de Regatas.xlsx
+++ b/Casos de Regatas.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b358109354d87fd/Diplomaturas/01. Inteligencia Artificial Aplicada/Materias/04. Procesamiento de Lenguaje Natural/99. DIIA-PLN-TP-Final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="11_2C447A9E1C490587C5EB8AD627D4F21B5C78B259" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D593CC31-402B-2B4B-B0DA-6A9493322C0C}"/>
+  <xr:revisionPtr revIDLastSave="539" documentId="11_2C447A9E1C490587C5EB8AD627D4F21B5C78B259" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2DEAA62-19ED-A044-8B23-55F199894BB5}"/>
   <bookViews>
-    <workbookView xWindow="33680" yWindow="1940" windowWidth="33660" windowHeight="17360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="17460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Casos de Regatas y sus Títulos" sheetId="1" r:id="rId1"/>
     <sheet name="Resultados" sheetId="2" r:id="rId2"/>
     <sheet name="Análisis" sheetId="3" r:id="rId3"/>
+    <sheet name="Comentarios generales" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="109">
   <si>
     <t>ID</t>
   </si>
@@ -1004,95 +1005,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: B perdió su derecho de paso al virar. Mientras un barco vira, debe mantenerse alejado de los demás .
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Decisión</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Penalizar a B.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hechos</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: X frena en la marca para atrapar a B. B choca con X .
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Norma</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Regla 11 y 18.2 según TR CALL J9 .
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rationale</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: X es el barco con derecho de paso y espacio de marca. B (barlovento) debe mantenerse alejada de X independientemente de la táctica de equipo de X .
 </t>
     </r>
     <r>
@@ -1496,12 +1408,6 @@
     <t>Falla</t>
   </si>
   <si>
-    <t>CoT - ES: El resultado es correcto, pero el modelo alucina en el rationale y en la regla aplicable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoT - ES: Solo aplica la regla 11 pero no aplica la regla 16.1 </t>
-  </si>
-  <si>
     <t>CoT - EN:</t>
   </si>
   <si>
@@ -1514,31 +1420,244 @@
     <t xml:space="preserve">CoT - ES: </t>
   </si>
   <si>
-    <t>CoT - ES: Alucina en el rationale y con las reglas</t>
-  </si>
-  <si>
-    <t>CoT - ES: El modelo interpreta el escenario de manera particular (asume que el barco B completó la virada)</t>
-  </si>
-  <si>
-    <t>CoT - ES: No explicita todas las reglas que deberían considerarse</t>
-  </si>
-  <si>
-    <t>CoT - ES: El modelo asume que el barco Y vira y choca</t>
-  </si>
-  <si>
-    <t>CoT - ES: Las reglas mencionadas no se ajustan al Ground Thruth</t>
-  </si>
-  <si>
-    <t>CoT - ES: Identifica bien la regla, pero interpreta mal los puntos de aplicación</t>
-  </si>
-  <si>
-    <t>CoT - ES: El modelo asume que B choca, y toma la decisión correcta penalizando. La reglas de aplicación tienen sentido</t>
-  </si>
-  <si>
-    <t>CoT - ES: El análisis de modelo es correcto, pero hay una "zona gris" del escenario que probablemente causa confusión</t>
-  </si>
-  <si>
-    <t>CoT - ES: Razonamiento incorrecto</t>
+    <t>Llama3</t>
+  </si>
+  <si>
+    <t>Qwen 2.5</t>
+  </si>
+  <si>
+    <t>CoT - ES: Respuesta correcta. Las reglas de aplicación no son las mencionadas en el GT. Referencias a reglas en inglés</t>
+  </si>
+  <si>
+    <t>CoT - ES: El razonamiento no es correcto</t>
+  </si>
+  <si>
+    <t>CoT - ES: El razonamiento y las reglas mencionadas no son precisas</t>
+  </si>
+  <si>
+    <t>CoT - ES: El modelo asume que B vira y decide su penalizacion</t>
+  </si>
+  <si>
+    <t>CoT - ES: Menciona regla correcta, pero sección incorrecta</t>
+  </si>
+  <si>
+    <t>CoT - ES: El modelo asume que Y vira y lo penaliza</t>
+  </si>
+  <si>
+    <t>CoT - ES: No identifica que B está en una penalización</t>
+  </si>
+  <si>
+    <t>CoT - ES: Hay un razonmiento especial en el caso, que puede asociarse a reglas de negocio</t>
+  </si>
+  <si>
+    <t>CoT - ES: El modelo asume que debe penalizar a algun barco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ok </t>
+  </si>
+  <si>
+    <t>CoT - ES: Razonamiento correcto</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hechos</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: X frena en la marca para atrapar a B. B choca con X .
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Norma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Regla 11 y 18.2 según TR CALL J9 .
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: X es el barco con derecho de paso y espacio de marca. B (barlovento) debe mantenerse alejada de X independientemente de la táctica de equipo de X .
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decisión</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Penalizar a X.</t>
+    </r>
+  </si>
+  <si>
+    <t>CoT - ES:  Situacion compleja, tal vez es necesario profundizar en instrucciones para el modelo</t>
+  </si>
+  <si>
+    <t>CoT - ES: Reglas diferentes</t>
+  </si>
+  <si>
+    <t>CoT - ES: Alucina con las identificacions de los barcos</t>
+  </si>
+  <si>
+    <t>CoT - System Prompt 
+en Español</t>
+  </si>
+  <si>
+    <t>CoT - System Prompt 
+en Inglés</t>
+  </si>
+  <si>
+    <t>CoT - EN: Confunde los nombres de los barcos</t>
+  </si>
+  <si>
+    <t>CoT - EN: Idem en español</t>
+  </si>
+  <si>
+    <t>CoT - EN:Hace un razonamieno claro, pero erra la decisión</t>
+  </si>
+  <si>
+    <t>CoT - EN: Decide penalizar a Y</t>
+  </si>
+  <si>
+    <t>CoT - EN: Penaliza al barco erroneo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ok. </t>
+  </si>
+  <si>
+    <t>CoT - EN: Identifica al barco responsable, pero no se da cuenta de agregar una nueva penalizacion</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>CoT - EN: Menciona reglas diferentes, pero responde bien</t>
+  </si>
+  <si>
+    <t>CoT - EN: Decide la penalizacion de B</t>
+  </si>
+  <si>
+    <t>CoT - EN: Alucina con nombres de barcos y erra el razonamiento</t>
+  </si>
+  <si>
+    <t>CoT - EN: la descripcion del escenario puede ser determinante en el resultado</t>
+  </si>
+  <si>
+    <t>FS CoT - System Prompt 
+en Español</t>
+  </si>
+  <si>
+    <t>FS CoT - System Prompt 
+en Inglés</t>
+  </si>
+  <si>
+    <t>Evaluacion con Llama3</t>
+  </si>
+  <si>
+    <t>Evaluacion con Qwen</t>
+  </si>
+  <si>
+    <t>FS CoT - ES:Razonamiento correcto</t>
+  </si>
+  <si>
+    <t>FS CoT - ES:Penaliza correctamente a B, pero tambien penaliza a Y de manera incorrecta</t>
+  </si>
+  <si>
+    <t>FS CoT - ES: Correcto, pero confunde reglas</t>
+  </si>
+  <si>
+    <t>En español FS CoT es sensiblemente mas lento</t>
+  </si>
+  <si>
+    <t>Añlgunos casos presentan una complejidad por "reglas de negocio" que el modelo no puede resolver. Hay oportunidad de mejora con el system prompt</t>
+  </si>
+  <si>
+    <t>FS CoT - ES:Penaliza a Y</t>
+  </si>
+  <si>
+    <t>FS CoT - ES: se complica con el razonamiento</t>
+  </si>
+  <si>
+    <t>FS CoT - ES: No identifica que B está cumoliendo una penalización</t>
+  </si>
+  <si>
+    <t>Qwen</t>
+  </si>
+  <si>
+    <t>El razonamiento parece ser mas completo</t>
+  </si>
+  <si>
+    <t>En general es mas lento para responer</t>
+  </si>
+  <si>
+    <t>El razonamiento y el detalle para responder es mucho mejor. Identifica mejor las reglas a aplicar</t>
+  </si>
+  <si>
+    <t>Generales</t>
+  </si>
+  <si>
+    <t>A veces los modelos "renombran" a los barcos. Hay que resolver eso para evitar confusiones</t>
+  </si>
+  <si>
+    <t>FS CoT - ES: Falla al no penalizar a Y porque asume que esta ahí de manera accidental</t>
   </si>
 </sst>
 </file>
@@ -1589,7 +1708,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1602,8 +1721,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1744,12 +1881,74 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1764,6 +1963,43 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1773,8 +2009,20 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1782,12 +2030,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1797,12 +2039,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1812,25 +2048,59 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2224,7 +2494,7 @@
         <v>17</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="70" x14ac:dyDescent="0.15">
@@ -2238,7 +2508,7 @@
         <v>30</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="70" x14ac:dyDescent="0.15">
@@ -2252,7 +2522,7 @@
         <v>31</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="56" x14ac:dyDescent="0.15">
@@ -2266,7 +2536,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="70" x14ac:dyDescent="0.15">
@@ -2280,7 +2550,7 @@
         <v>33</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2290,784 +2560,1469 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CDA499-0016-9E48-AD79-F5B2F70F2B84}">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A2:K64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="85.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="85.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="23.5" customWidth="1"/>
+    <col min="9" max="9" width="18.5" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+    <col min="11" max="11" width="34.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A1" s="1"/>
-    </row>
-    <row r="3" spans="1:7" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="10" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="B2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+    </row>
+    <row r="3" spans="1:11" ht="29" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="20"/>
+      <c r="F3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B4" s="11"/>
-      <c r="C4" s="9" t="s">
+      <c r="G3" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="20"/>
+      <c r="K3" s="22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A4" s="28"/>
+      <c r="B4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="D4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="13"/>
-    </row>
-    <row r="5" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B5" s="14">
+      <c r="F4" s="23"/>
+      <c r="G4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="23"/>
+    </row>
+    <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.15">
+      <c r="A5" s="29">
         <v>1</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="B5" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="25"/>
+      <c r="I5" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="25"/>
+      <c r="K5" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A6" s="30"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="30"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="31"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A9" s="29">
+        <v>2</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="27" t="s">
+      <c r="C9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="17"/>
+      <c r="K9" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A10" s="30"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A11" s="30"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B6" s="15"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="27" t="s">
+    <row r="12" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A12" s="31"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A13" s="29">
+        <v>3</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="17"/>
+      <c r="K13" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B7" s="15"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B8" s="16"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B9" s="14">
-        <v>2</v>
-      </c>
-      <c r="C9" s="17" t="s">
+    <row r="14" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A14" s="30"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="27" t="s">
+    </row>
+    <row r="15" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A15" s="30"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A16" s="31"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="9" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B10" s="15"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="27" t="s">
+      <c r="G16" s="13"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A17" s="29">
+        <v>4</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B11" s="15"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B12" s="16"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B13" s="14">
-        <v>3</v>
-      </c>
-      <c r="C13" s="17" t="s">
+    <row r="18" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A18" s="30"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A19" s="30"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A20" s="31"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A21" s="32">
+        <v>5</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B14" s="15"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="27" t="s">
+      <c r="E21" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="14"/>
+      <c r="K21" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B15" s="15"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B16" s="16"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="28" x14ac:dyDescent="0.15">
-      <c r="B17" s="14">
-        <v>4</v>
-      </c>
-      <c r="C17" s="17" t="s">
+    <row r="22" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A22" s="33"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B18" s="15"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="27" t="s">
+    </row>
+    <row r="23" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A23" s="33"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A24" s="34"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A25" s="32">
+        <v>6</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="14"/>
+      <c r="K25" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B19" s="15"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B20" s="16"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B21" s="19">
-        <v>5</v>
-      </c>
-      <c r="C21" s="17" t="s">
+    <row r="26" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A26" s="33"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A27" s="33"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A28" s="36"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" s="13"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A29" s="35">
+        <v>7</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B22" s="20"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="27" t="s">
+      <c r="C29" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J29" s="14"/>
+      <c r="K29" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B23" s="20"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B24" s="21"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B25" s="19">
-        <v>6</v>
-      </c>
-      <c r="C25" s="17" t="s">
+    <row r="30" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A30" s="33"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="13"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A31" s="33"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="13"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A32" s="36"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="13"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A33" s="35">
+        <v>8</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B26" s="20"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="27" t="s">
+      <c r="C33" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="14"/>
+      <c r="K33" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B27" s="20"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B28" s="23"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B29" s="24">
-        <v>7</v>
-      </c>
-      <c r="C29" s="17" t="s">
+    <row r="34" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A34" s="33"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B30" s="20"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="27" t="s">
+    </row>
+    <row r="35" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A35" s="33"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35" s="13"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A36" s="36"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G36" s="13"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A37" s="35">
+        <v>9</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J37" s="14"/>
+      <c r="K37" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B31" s="20"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B32" s="23"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B33" s="24">
-        <v>8</v>
-      </c>
-      <c r="C33" s="17" t="s">
+    <row r="38" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A38" s="33"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G38" s="13"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B34" s="20"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="27" t="s">
+    </row>
+    <row r="39" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A39" s="33"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A40" s="36"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" s="13"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A41" s="35">
+        <v>10</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J41" s="14"/>
+      <c r="K41" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B35" s="20"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B36" s="23"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" ht="28" x14ac:dyDescent="0.15">
-      <c r="B37" s="24">
-        <v>9</v>
-      </c>
-      <c r="C37" s="17" t="s">
+    <row r="42" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A42" s="33"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" s="13"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="33"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G43" s="13"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="36"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G44" s="13"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A45" s="35">
+        <v>11</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J45" s="14"/>
+      <c r="K45" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A46" s="33"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G46" s="13"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A47" s="33"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G47" s="13"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A48" s="36"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G48" s="13"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A49" s="35">
+        <v>12</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J49" s="14"/>
+      <c r="K49" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A50" s="33"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G50" s="13"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A51" s="33"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G51" s="13"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A52" s="36"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G52" s="13"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A53" s="35">
+        <v>13</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B38" s="20"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="27" t="s">
+      <c r="D53" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J53" s="14"/>
+      <c r="K53" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B39" s="20"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B40" s="23"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" ht="28" x14ac:dyDescent="0.15">
-      <c r="B41" s="24">
-        <v>10</v>
-      </c>
-      <c r="C41" s="17" t="s">
+    <row r="54" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A54" s="33"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G54" s="13"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B42" s="20"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="27" t="s">
+    </row>
+    <row r="55" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A55" s="33"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G55" s="13"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A56" s="36"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="13"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A57" s="35">
+        <v>14</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E57" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G57" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J57" s="14"/>
+      <c r="K57" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B43" s="20"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B44" s="23"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B45" s="24">
-        <v>11</v>
-      </c>
-      <c r="C45" s="17" t="s">
+    <row r="58" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A58" s="33"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G58" s="13"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B46" s="20"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="27" t="s">
+    </row>
+    <row r="59" spans="1:11" ht="42" x14ac:dyDescent="0.15">
+      <c r="A59" s="33"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G59" s="13"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A60" s="36"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G60" s="13"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A61" s="35">
+        <v>15</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G61" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="J61" s="14"/>
+      <c r="K61" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B47" s="20"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B48" s="23"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B49" s="24">
-        <v>12</v>
-      </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B50" s="20"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B51" s="20"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B52" s="23"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B53" s="24">
-        <v>13</v>
-      </c>
-      <c r="C53" s="17"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B54" s="20"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B55" s="20"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B56" s="23"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B57" s="24">
-        <v>14</v>
-      </c>
-      <c r="C57" s="17"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B58" s="20"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B59" s="20"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B60" s="23"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B61" s="24">
-        <v>15</v>
-      </c>
-      <c r="C61" s="17"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B62" s="20"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B63" s="20"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B64" s="23"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="27" t="s">
-        <v>60</v>
+    <row r="62" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A62" s="33"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G62" s="13"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A63" s="33"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G63" s="13"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="14" x14ac:dyDescent="0.15">
+      <c r="A64" s="36"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G64" s="15"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
+      <c r="K64" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="79">
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="F9:F12"/>
+  <mergeCells count="144">
+    <mergeCell ref="A61:A64"/>
+    <mergeCell ref="B61:B64"/>
+    <mergeCell ref="C61:C64"/>
+    <mergeCell ref="D61:D64"/>
+    <mergeCell ref="E61:E64"/>
+    <mergeCell ref="A57:A60"/>
     <mergeCell ref="B57:B60"/>
     <mergeCell ref="C57:C60"/>
     <mergeCell ref="D57:D60"/>
     <mergeCell ref="E57:E60"/>
-    <mergeCell ref="F57:F60"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="C61:C64"/>
-    <mergeCell ref="D61:D64"/>
-    <mergeCell ref="E61:E64"/>
-    <mergeCell ref="F61:F64"/>
+    <mergeCell ref="A53:A56"/>
+    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="C53:C56"/>
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="E53:E56"/>
+    <mergeCell ref="A49:A52"/>
     <mergeCell ref="B49:B52"/>
     <mergeCell ref="C49:C52"/>
     <mergeCell ref="D49:D52"/>
     <mergeCell ref="E49:E52"/>
-    <mergeCell ref="F49:F52"/>
-    <mergeCell ref="B53:B56"/>
-    <mergeCell ref="C53:C56"/>
-    <mergeCell ref="D53:D56"/>
-    <mergeCell ref="E53:E56"/>
-    <mergeCell ref="F53:F56"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="C41:C44"/>
-    <mergeCell ref="D41:D44"/>
-    <mergeCell ref="E41:E44"/>
-    <mergeCell ref="F41:F44"/>
+    <mergeCell ref="A45:A48"/>
     <mergeCell ref="B45:B48"/>
     <mergeCell ref="C45:C48"/>
     <mergeCell ref="D45:D48"/>
     <mergeCell ref="E45:E48"/>
-    <mergeCell ref="F45:F48"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="E41:E44"/>
+    <mergeCell ref="D41:D44"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="C37:C40"/>
+    <mergeCell ref="D37:D40"/>
+    <mergeCell ref="E37:E40"/>
+    <mergeCell ref="A33:A36"/>
     <mergeCell ref="B33:B36"/>
     <mergeCell ref="C33:C36"/>
     <mergeCell ref="D33:D36"/>
     <mergeCell ref="E33:E36"/>
-    <mergeCell ref="F33:F36"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="C37:C40"/>
-    <mergeCell ref="D37:D40"/>
-    <mergeCell ref="E37:E40"/>
-    <mergeCell ref="F37:F40"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="D29:D32"/>
+    <mergeCell ref="E29:E32"/>
+    <mergeCell ref="A25:A28"/>
     <mergeCell ref="B25:B28"/>
     <mergeCell ref="C25:C28"/>
     <mergeCell ref="D25:D28"/>
     <mergeCell ref="E25:E28"/>
-    <mergeCell ref="F25:F28"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="D29:D32"/>
-    <mergeCell ref="E29:E32"/>
-    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="A17:A20"/>
     <mergeCell ref="B17:B20"/>
     <mergeCell ref="C17:C20"/>
     <mergeCell ref="D17:D20"/>
     <mergeCell ref="E17:E20"/>
-    <mergeCell ref="F17:F20"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="D13:D16"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="F13:F16"/>
     <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="H9:H12"/>
+    <mergeCell ref="I9:I12"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="G13:G16"/>
+    <mergeCell ref="H13:H16"/>
+    <mergeCell ref="I13:I16"/>
+    <mergeCell ref="J13:J16"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="G25:G28"/>
+    <mergeCell ref="H25:H28"/>
+    <mergeCell ref="I25:I28"/>
+    <mergeCell ref="J25:J28"/>
+    <mergeCell ref="G29:G32"/>
+    <mergeCell ref="H29:H32"/>
+    <mergeCell ref="I29:I32"/>
+    <mergeCell ref="J29:J32"/>
+    <mergeCell ref="G17:G20"/>
+    <mergeCell ref="H17:H20"/>
+    <mergeCell ref="I17:I20"/>
+    <mergeCell ref="J17:J20"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="G41:G44"/>
+    <mergeCell ref="H41:H44"/>
+    <mergeCell ref="I41:I44"/>
+    <mergeCell ref="J41:J44"/>
+    <mergeCell ref="G45:G48"/>
+    <mergeCell ref="H45:H48"/>
+    <mergeCell ref="I45:I48"/>
+    <mergeCell ref="J45:J48"/>
+    <mergeCell ref="G33:G36"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="I33:I36"/>
+    <mergeCell ref="J33:J36"/>
+    <mergeCell ref="G37:G40"/>
+    <mergeCell ref="H37:H40"/>
+    <mergeCell ref="I37:I40"/>
+    <mergeCell ref="J37:J40"/>
+    <mergeCell ref="G57:G60"/>
+    <mergeCell ref="H57:H60"/>
+    <mergeCell ref="I57:I60"/>
+    <mergeCell ref="J57:J60"/>
+    <mergeCell ref="G61:G64"/>
+    <mergeCell ref="H61:H64"/>
+    <mergeCell ref="I61:I64"/>
+    <mergeCell ref="J61:J64"/>
+    <mergeCell ref="G49:G52"/>
+    <mergeCell ref="H49:H52"/>
+    <mergeCell ref="I49:I52"/>
+    <mergeCell ref="J49:J52"/>
+    <mergeCell ref="G53:G56"/>
+    <mergeCell ref="H53:H56"/>
+    <mergeCell ref="I53:I56"/>
+    <mergeCell ref="J53:J56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3075,21 +4030,303 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED012409-1330-4547-82DA-5BA50D4F7AB8}">
-  <dimension ref="E6:K13"/>
+  <dimension ref="B2:L13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="4" max="4" width="5.1640625" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" customWidth="1"/>
+    <col min="10" max="10" width="4.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B2" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="40"/>
+      <c r="H2" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="48"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+    </row>
+    <row r="4" spans="2:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="43"/>
+      <c r="H4" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="51"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="51"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B5" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="41"/>
+      <c r="E5" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="49"/>
+      <c r="K5" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="52" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B6" s="45">
+        <f>COUNTIF(Resultados!B$5:B$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="C6" s="45">
+        <f>COUNTIF(Resultados!B$5:B$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="41"/>
+      <c r="E6" s="45">
+        <f>COUNTIF(Resultados!C$5:C$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="F6" s="45">
+        <f>COUNTIF(Resultados!C$5:C$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="H6" s="53">
+        <f>COUNTIF(Resultados!G$5:G$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I6" s="53">
+        <f>COUNTIF(Resultados!G$5:G$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J6" s="49"/>
+      <c r="K6" s="53">
+        <f>COUNTIF(Resultados!J$5:J$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="53">
+        <f>COUNTIF(Resultados!J$5:J$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+    </row>
+    <row r="9" spans="2:12" ht="28" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="43"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="43"/>
+      <c r="H9" s="50" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="51"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="51"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="41"/>
+      <c r="E10" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="49"/>
+      <c r="K10" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="52" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B11" s="45">
+        <f>COUNTIF(Resultados!D$5:D$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="C11" s="45">
+        <f>COUNTIF(Resultados!D$5:D$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="D11" s="41"/>
+      <c r="E11" s="45">
+        <f>COUNTIF(Resultados!E$5:E$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="F11" s="45">
+        <f>COUNTIF(Resultados!E$5:E$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="H11" s="53">
+        <f>COUNTIF(Resultados!I$5:I$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="I11" s="53">
+        <f>COUNTIF(Resultados!I$5:I$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="J11" s="49"/>
+      <c r="K11" s="53">
+        <f>COUNTIF(Resultados!L$5:L$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="53">
+        <f>COUNTIF(Resultados!L$5:L$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="J13" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC011E3-ACF6-1543-9486-00BE9BEF8B0A}">
+  <dimension ref="D5:D28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="6" spans="5:11" x14ac:dyDescent="0.15">
-      <c r="E6" s="28">
-        <f>COUNTIF(Resultados!C$5:C$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="F6" s="28">
-        <f>COUNTIF(Resultados!C$5:C$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="13" spans="5:11" x14ac:dyDescent="0.15">
-      <c r="K13" s="28"/>
+    <row r="5" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D5" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D7" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D9" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D15" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D17" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D19" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D21" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D26" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.15">
+      <c r="D28" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Casos de Regatas.xlsx
+++ b/Casos de Regatas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b358109354d87fd/Diplomaturas/01. Inteligencia Artificial Aplicada/Materias/04. Procesamiento de Lenguaje Natural/99. DIIA-PLN-TP-Final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="539" documentId="11_2C447A9E1C490587C5EB8AD627D4F21B5C78B259" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2DEAA62-19ED-A044-8B23-55F199894BB5}"/>
+  <xr:revisionPtr revIDLastSave="578" documentId="11_2C447A9E1C490587C5EB8AD627D4F21B5C78B259" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68382120-6E42-B04F-8967-EA922F9CED2A}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="17460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Casos de Regatas y sus Títulos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="106">
   <si>
     <t>ID</t>
   </si>
@@ -1453,9 +1453,6 @@
     <t>CoT - ES: El modelo asume que debe penalizar a algun barco</t>
   </si>
   <si>
-    <t xml:space="preserve">Ok </t>
-  </si>
-  <si>
     <t>CoT - ES: Razonamiento correcto</t>
   </si>
   <si>
@@ -1580,13 +1577,7 @@
     <t>CoT - EN: Penaliza al barco erroneo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ok. </t>
-  </si>
-  <si>
     <t>CoT - EN: Identifica al barco responsable, pero no se da cuenta de agregar una nueva penalizacion</t>
-  </si>
-  <si>
-    <t>OK</t>
   </si>
   <si>
     <t>CoT - EN: Menciona reglas diferentes, pero responde bien</t>
@@ -1948,7 +1939,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2016,9 +2007,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2494,7 +2482,7 @@
         <v>17</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="70" x14ac:dyDescent="0.15">
@@ -2586,13 +2574,13 @@
       <c r="G2" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" spans="1:11" ht="29" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="19" t="s">
@@ -2619,7 +2607,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A4" s="28"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="6" t="s">
         <v>48</v>
       </c>
@@ -2648,19 +2636,19 @@
       <c r="K4" s="23"/>
     </row>
     <row r="5" spans="1:11" ht="28" x14ac:dyDescent="0.15">
-      <c r="A5" s="29">
+      <c r="A5" s="28">
         <v>1</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="37" t="s">
+      <c r="C5" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="36" t="s">
         <v>53</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -2669,23 +2657,27 @@
       <c r="G5" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="25"/>
-      <c r="I5" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="25"/>
+      <c r="H5" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="36" t="s">
+        <v>53</v>
+      </c>
       <c r="K5" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A6" s="30"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="13"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="17"/>
@@ -2696,13 +2688,13 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="30"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="13"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="17"/>
@@ -2713,7 +2705,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="31"/>
+      <c r="A8" s="30"/>
       <c r="B8" s="13"/>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -2730,7 +2722,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>2</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -2751,23 +2743,27 @@
       <c r="G9" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="17"/>
+      <c r="H9" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I9" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="17"/>
+      <c r="J9" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="K9" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A10" s="30"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="13"/>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
       <c r="E10" s="17"/>
       <c r="F10" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="17"/>
@@ -2778,13 +2774,13 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A11" s="30"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="13"/>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="17"/>
@@ -2795,7 +2791,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A12" s="31"/>
+      <c r="A12" s="30"/>
       <c r="B12" s="13"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -2812,7 +2808,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A13" s="29">
+      <c r="A13" s="28">
         <v>3</v>
       </c>
       <c r="B13" s="13" t="s">
@@ -2833,23 +2829,27 @@
       <c r="G13" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="17"/>
+      <c r="H13" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I13" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J13" s="17"/>
+      <c r="J13" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="K13" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A14" s="30"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="13"/>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="17"/>
@@ -2860,13 +2860,13 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A15" s="30"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="13"/>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="17"/>
@@ -2877,7 +2877,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A16" s="31"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="13"/>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -2894,7 +2894,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A17" s="29">
+      <c r="A17" s="28">
         <v>4</v>
       </c>
       <c r="B17" s="13" t="s">
@@ -2915,23 +2915,27 @@
       <c r="G17" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H17" s="17"/>
+      <c r="H17" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="I17" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J17" s="17"/>
+      <c r="J17" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="K17" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A18" s="30"/>
+      <c r="A18" s="29"/>
       <c r="B18" s="13"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="17"/>
@@ -2942,13 +2946,13 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A19" s="30"/>
+      <c r="A19" s="29"/>
       <c r="B19" s="13"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="17"/>
@@ -2959,7 +2963,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A20" s="31"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="13"/>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -2976,7 +2980,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A21" s="32">
+      <c r="A21" s="31">
         <v>5</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -2997,23 +3001,27 @@
       <c r="G21" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="14"/>
+      <c r="H21" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I21" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J21" s="14"/>
+      <c r="J21" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="K21" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A22" s="33"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="13"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="14"/>
@@ -3024,13 +3032,13 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A23" s="33"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="13"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="14"/>
@@ -3041,7 +3049,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A24" s="34"/>
+      <c r="A24" s="33"/>
       <c r="B24" s="13"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
@@ -3058,7 +3066,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A25" s="32">
+      <c r="A25" s="31">
         <v>6</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -3079,23 +3087,27 @@
       <c r="G25" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="14"/>
+      <c r="H25" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="I25" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J25" s="14"/>
+      <c r="J25" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="K25" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A26" s="33"/>
+      <c r="A26" s="32"/>
       <c r="B26" s="13"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G26" s="13"/>
       <c r="H26" s="14"/>
@@ -3106,7 +3118,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A27" s="33"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="13"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -3123,7 +3135,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A28" s="36"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="13"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -3140,14 +3152,14 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A29" s="35">
+      <c r="A29" s="34">
         <v>7</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>54</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>54</v>
@@ -3161,23 +3173,27 @@
       <c r="G29" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H29" s="14"/>
+      <c r="H29" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="I29" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J29" s="14"/>
+      <c r="J29" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="K29" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A30" s="33"/>
+      <c r="A30" s="32"/>
       <c r="B30" s="13"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G30" s="13"/>
       <c r="H30" s="14"/>
@@ -3188,13 +3204,13 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A31" s="33"/>
+      <c r="A31" s="32"/>
       <c r="B31" s="13"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G31" s="13"/>
       <c r="H31" s="14"/>
@@ -3205,7 +3221,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A32" s="36"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="13"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -3222,14 +3238,14 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A33" s="35">
+      <c r="A33" s="34">
         <v>8</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>54</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>54</v>
@@ -3243,23 +3259,27 @@
       <c r="G33" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H33" s="14"/>
+      <c r="H33" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="I33" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J33" s="14"/>
+      <c r="J33" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="K33" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A34" s="33"/>
+      <c r="A34" s="32"/>
       <c r="B34" s="13"/>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G34" s="13"/>
       <c r="H34" s="14"/>
@@ -3270,7 +3290,7 @@
       </c>
     </row>
     <row r="35" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A35" s="33"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="13"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
@@ -3287,7 +3307,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A36" s="36"/>
+      <c r="A36" s="35"/>
       <c r="B36" s="13"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -3304,7 +3324,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A37" s="35">
+      <c r="A37" s="34">
         <v>9</v>
       </c>
       <c r="B37" s="13" t="s">
@@ -3325,23 +3345,27 @@
       <c r="G37" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H37" s="14"/>
+      <c r="H37" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="I37" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J37" s="14"/>
+      <c r="J37" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="K37" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A38" s="33"/>
+      <c r="A38" s="32"/>
       <c r="B38" s="13"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G38" s="13"/>
       <c r="H38" s="14"/>
@@ -3352,7 +3376,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A39" s="33"/>
+      <c r="A39" s="32"/>
       <c r="B39" s="13"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
@@ -3369,7 +3393,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A40" s="36"/>
+      <c r="A40" s="35"/>
       <c r="B40" s="13"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
@@ -3386,38 +3410,42 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A41" s="35">
+      <c r="A41" s="34">
         <v>10</v>
       </c>
       <c r="B41" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G41" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H41" s="14"/>
+      <c r="H41" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I41" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J41" s="14"/>
+      <c r="J41" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="K41" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A42" s="33"/>
+      <c r="A42" s="32"/>
       <c r="B42" s="13"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
@@ -3434,7 +3462,7 @@
       </c>
     </row>
     <row r="43" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="33"/>
+      <c r="A43" s="32"/>
       <c r="B43" s="13"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -3451,7 +3479,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="36"/>
+      <c r="A44" s="35"/>
       <c r="B44" s="13"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
@@ -3468,7 +3496,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A45" s="35">
+      <c r="A45" s="34">
         <v>11</v>
       </c>
       <c r="B45" s="13" t="s">
@@ -3484,28 +3512,32 @@
         <v>53</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H45" s="14"/>
+      <c r="H45" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I45" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J45" s="14"/>
+      <c r="J45" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="K45" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A46" s="33"/>
+      <c r="A46" s="32"/>
       <c r="B46" s="13"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G46" s="13"/>
       <c r="H46" s="14"/>
@@ -3516,7 +3548,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A47" s="33"/>
+      <c r="A47" s="32"/>
       <c r="B47" s="13"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -3533,7 +3565,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A48" s="36"/>
+      <c r="A48" s="35"/>
       <c r="B48" s="13"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -3550,7 +3582,7 @@
       </c>
     </row>
     <row r="49" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A49" s="35">
+      <c r="A49" s="34">
         <v>12</v>
       </c>
       <c r="B49" s="13" t="s">
@@ -3566,28 +3598,32 @@
         <v>53</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H49" s="14"/>
+      <c r="H49" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I49" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J49" s="14"/>
+      <c r="J49" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="K49" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A50" s="33"/>
+      <c r="A50" s="32"/>
       <c r="B50" s="13"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G50" s="13"/>
       <c r="H50" s="14"/>
@@ -3598,7 +3634,7 @@
       </c>
     </row>
     <row r="51" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A51" s="33"/>
+      <c r="A51" s="32"/>
       <c r="B51" s="13"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -3615,7 +3651,7 @@
       </c>
     </row>
     <row r="52" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A52" s="36"/>
+      <c r="A52" s="35"/>
       <c r="B52" s="13"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -3632,7 +3668,7 @@
       </c>
     </row>
     <row r="53" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A53" s="35">
+      <c r="A53" s="34">
         <v>13</v>
       </c>
       <c r="B53" s="13" t="s">
@@ -3648,28 +3684,32 @@
         <v>54</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H53" s="14"/>
+      <c r="H53" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="I53" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J53" s="14"/>
+      <c r="J53" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="K53" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A54" s="33"/>
+      <c r="A54" s="32"/>
       <c r="B54" s="13"/>
       <c r="C54" s="14"/>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G54" s="13"/>
       <c r="H54" s="14"/>
@@ -3680,7 +3720,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A55" s="33"/>
+      <c r="A55" s="32"/>
       <c r="B55" s="13"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -3697,7 +3737,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A56" s="36"/>
+      <c r="A56" s="35"/>
       <c r="B56" s="13"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -3714,7 +3754,7 @@
       </c>
     </row>
     <row r="57" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A57" s="35">
+      <c r="A57" s="34">
         <v>14</v>
       </c>
       <c r="B57" s="13" t="s">
@@ -3730,28 +3770,32 @@
         <v>53</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H57" s="14"/>
+      <c r="H57" s="14" t="s">
+        <v>54</v>
+      </c>
       <c r="I57" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="14"/>
+      <c r="J57" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="K57" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A58" s="33"/>
+      <c r="A58" s="32"/>
       <c r="B58" s="13"/>
       <c r="C58" s="14"/>
       <c r="D58" s="14"/>
       <c r="E58" s="14"/>
       <c r="F58" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G58" s="13"/>
       <c r="H58" s="14"/>
@@ -3762,7 +3806,7 @@
       </c>
     </row>
     <row r="59" spans="1:11" ht="42" x14ac:dyDescent="0.15">
-      <c r="A59" s="33"/>
+      <c r="A59" s="32"/>
       <c r="B59" s="13"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
@@ -3775,11 +3819,11 @@
       <c r="I59" s="14"/>
       <c r="J59" s="14"/>
       <c r="K59" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A60" s="36"/>
+      <c r="A60" s="35"/>
       <c r="B60" s="13"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
@@ -3796,7 +3840,7 @@
       </c>
     </row>
     <row r="61" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A61" s="35">
+      <c r="A61" s="34">
         <v>15</v>
       </c>
       <c r="B61" s="13" t="s">
@@ -3812,28 +3856,32 @@
         <v>54</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H61" s="14"/>
+      <c r="H61" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="I61" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="J61" s="14"/>
+      <c r="J61" s="14" t="s">
+        <v>53</v>
+      </c>
       <c r="K61" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A62" s="33"/>
+      <c r="A62" s="32"/>
       <c r="B62" s="13"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
       <c r="E62" s="14"/>
       <c r="F62" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G62" s="13"/>
       <c r="H62" s="14"/>
@@ -3844,7 +3892,7 @@
       </c>
     </row>
     <row r="63" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A63" s="33"/>
+      <c r="A63" s="32"/>
       <c r="B63" s="13"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
@@ -3861,7 +3909,7 @@
       </c>
     </row>
     <row r="64" spans="1:11" ht="14" x14ac:dyDescent="0.15">
-      <c r="A64" s="36"/>
+      <c r="A64" s="35"/>
       <c r="B64" s="15"/>
       <c r="C64" s="16"/>
       <c r="D64" s="16"/>
@@ -4039,223 +4087,223 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B2" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="40"/>
-      <c r="H2" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="48"/>
+      <c r="B2" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="39"/>
+      <c r="H2" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="47"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
     </row>
     <row r="4" spans="2:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="42"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="43"/>
-      <c r="H4" s="50" t="s">
+      <c r="F4" s="42"/>
+      <c r="H4" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="50"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="51"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="51"/>
+      <c r="L4" s="50"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B5" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="41"/>
-      <c r="E5" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="49"/>
-      <c r="K5" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="52" t="s">
+      <c r="B5" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="40"/>
+      <c r="E5" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="48"/>
+      <c r="K5" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="51" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B6" s="45">
+      <c r="B6" s="44">
         <f>COUNTIF(Resultados!B$5:B$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
-        <v>0.73333333333333328</v>
-      </c>
-      <c r="C6" s="45">
+        <v>0.8</v>
+      </c>
+      <c r="C6" s="44">
         <f>COUNTIF(Resultados!B$5:B$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.2</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="45">
+      <c r="D6" s="40"/>
+      <c r="E6" s="44">
         <f>COUNTIF(Resultados!C$5:C$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
-        <v>0.46666666666666667</v>
-      </c>
-      <c r="F6" s="45">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="F6" s="44">
         <f>COUNTIF(Resultados!C$5:C$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.46666666666666667</v>
       </c>
-      <c r="H6" s="53">
+      <c r="H6" s="52">
         <f>COUNTIF(Resultados!G$5:G$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="52">
         <f>COUNTIF(Resultados!G$5:G$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="J6" s="49"/>
-      <c r="K6" s="53">
-        <f>COUNTIF(Resultados!J$5:J$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="53">
-        <f>COUNTIF(Resultados!J$5:J$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
-        <v>0</v>
+      <c r="J6" s="48"/>
+      <c r="K6" s="52">
+        <f>COUNTIF(Resultados!H$5:H$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="L6" s="52">
+        <f>COUNTIF(Resultados!H$5:H$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.46666666666666667</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
     </row>
     <row r="9" spans="2:12" ht="28" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="43"/>
-      <c r="H9" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="51"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9" s="51"/>
+      <c r="B9" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="42"/>
+      <c r="H9" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="50"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="50"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B10" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="49"/>
-      <c r="K10" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" s="52" t="s">
+      <c r="B10" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="40"/>
+      <c r="E10" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J10" s="48"/>
+      <c r="K10" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="51" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B11" s="45">
+      <c r="B11" s="44">
         <f>COUNTIF(Resultados!D$5:D$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.46666666666666667</v>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="44">
         <f>COUNTIF(Resultados!D$5:D$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="45">
+      <c r="D11" s="40"/>
+      <c r="E11" s="44">
         <f>COUNTIF(Resultados!E$5:E$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.46666666666666667</v>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="44">
         <f>COUNTIF(Resultados!E$5:E$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.53333333333333333</v>
       </c>
-      <c r="H11" s="53">
+      <c r="H11" s="52">
         <f>COUNTIF(Resultados!I$5:I$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.73333333333333328</v>
       </c>
-      <c r="I11" s="53">
+      <c r="I11" s="52">
         <f>COUNTIF(Resultados!I$5:I$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
         <v>0.26666666666666666</v>
       </c>
-      <c r="J11" s="49"/>
-      <c r="K11" s="53">
-        <f>COUNTIF(Resultados!L$5:L$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="53">
-        <f>COUNTIF(Resultados!L$5:L$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
-        <v>0</v>
+      <c r="J11" s="48"/>
+      <c r="K11" s="52">
+        <f>COUNTIF(Resultados!J$5:J$64,"Ok")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L11" s="52">
+        <f>COUNTIF(Resultados!J$5:J$64,"Falla")/(COUNT('Casos de Regatas y sus Títulos'!A$3:A$17))</f>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.15">
@@ -4290,42 +4338,42 @@
     </row>
     <row r="7" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D7" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D9" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D15" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D17" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D19" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D21" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D26" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="4:4" x14ac:dyDescent="0.15">
       <c r="D28" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
